--- a/public/templates/template_guru.xlsx
+++ b/public/templates/template_guru.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="16">
   <si>
     <t>nama</t>
   </si>
@@ -47,7 +47,7 @@
     <t>081298765432</t>
   </si>
   <si>
-    <t>KETERANGAN:</t>
+    <t>BACA KETERANGAN !!!:</t>
   </si>
   <si>
     <t>- email: Username (wajib, unique)</t>
@@ -59,7 +59,10 @@
     <t>- Hapus baris 2 sebelum import!</t>
   </si>
   <si>
-    <t>- Disarankan menggunakan spreadsheet dibanding excel</t>
+    <t>- Disarankan menggunakan SPEADSHEET</t>
+  </si>
+  <si>
+    <t>- !!!(FORMAT COLUMN MENJADI TEKS BIASA)</t>
   </si>
 </sst>
 </file>
@@ -427,7 +430,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="true" style="0"/>
@@ -494,6 +497,11 @@
     <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
